--- a/JUEVES VIERNES SABADO.xlsx
+++ b/JUEVES VIERNES SABADO.xlsx
@@ -1140,7 +1140,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="4">
-        <v>120000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">

--- a/JUEVES VIERNES SABADO.xlsx
+++ b/JUEVES VIERNES SABADO.xlsx
@@ -1060,7 +1060,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="4">
-        <v>60000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">

--- a/JUEVES VIERNES SABADO.xlsx
+++ b/JUEVES VIERNES SABADO.xlsx
@@ -964,7 +964,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="4">
-        <v>6000</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
